--- a/testmoinhat.xlsx
+++ b/testmoinhat.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J13"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -473,7 +473,7 @@
         <v>Bot</v>
       </c>
       <c r="J2" t="str">
-        <v>13/8/2026</v>
+        <v>14/8/2026</v>
       </c>
     </row>
     <row r="3">
@@ -505,7 +505,7 @@
         <v>Bot</v>
       </c>
       <c r="J3" t="str">
-        <v>13/8/2026</v>
+        <v>14/8/2026</v>
       </c>
     </row>
     <row r="4">
@@ -537,7 +537,7 @@
         <v>Bot</v>
       </c>
       <c r="J4" t="str">
-        <v>13/8/2026</v>
+        <v>14/8/2026</v>
       </c>
     </row>
     <row r="5">
@@ -569,7 +569,7 @@
         <v>Bot</v>
       </c>
       <c r="J5" t="str">
-        <v>13/8/2026</v>
+        <v>14/8/2026</v>
       </c>
     </row>
     <row r="6">
@@ -601,7 +601,7 @@
         <v>Bot</v>
       </c>
       <c r="J6" t="str">
-        <v>13/8/2026</v>
+        <v>14/8/2026</v>
       </c>
     </row>
     <row r="7">
@@ -612,7 +612,7 @@
         <v>Project Launch</v>
       </c>
       <c r="C7" t="str">
-        <v>Tạo dự án mới với AI Planner</v>
+        <v>AI Planner creates project &amp; sprint</v>
       </c>
       <c r="D7" t="str">
         <v>PM</v>
@@ -621,19 +621,19 @@
         <v>Dự án và Sprint được tạo</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>Lỗi hiển thị receipt</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>Fail</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>ai-action-composer.spec.ts</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>Bot</v>
       </c>
       <c r="J7" t="str">
-        <v/>
+        <v>14/8/2026</v>
       </c>
     </row>
     <row r="8">
@@ -653,19 +653,19 @@
         <v>Task gán đúng người</v>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>Đúng như mong đợi</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>Pass</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>member-skill-assignment.spec.ts</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>Bot</v>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>14/8/2026</v>
       </c>
     </row>
     <row r="9">
@@ -685,19 +685,19 @@
         <v>Trạng thái cập nhật đúng</v>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>Đúng như mong đợi</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>Pass</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>rc-safety-workflow.spec.ts</v>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>Bot</v>
       </c>
       <c r="J9" t="str">
-        <v/>
+        <v>14/8/2026</v>
       </c>
     </row>
     <row r="10">
@@ -717,24 +717,120 @@
         <v>Dữ liệu được che giấu</v>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>Đúng như mong đợi</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>Pass</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>privacy-retention.spec.ts</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>Bot</v>
       </c>
       <c r="J10" t="str">
-        <v/>
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>TC_E2E_010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>AI Grounding</v>
+      </c>
+      <c r="C11" t="str">
+        <v>AI preserves exact selected-message grounding</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Member</v>
+      </c>
+      <c r="E11" t="str">
+        <v>AI đọc đúng message</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Fail do model timeout</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="H11" t="str">
+        <v>ai-native-grounded-surfaces.spec.ts</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Bot</v>
+      </c>
+      <c r="J11" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>TC_E2E_011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Demo Script</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Chạy xuyên suốt kịch bản 30p</v>
+      </c>
+      <c r="D12" t="str">
+        <v>All</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Hoàn thành đúng kịch bản</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Fail (Expected &lt;=8 members, got 10)</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="H12" t="str">
+        <v>demo-script-30-minutes.spec.ts</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Bot</v>
+      </c>
+      <c r="J12" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>TC_E2E_012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>General</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Tổng hợp 53 test cases khác</v>
+      </c>
+      <c r="D13" t="str">
+        <v>All</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Các luồng cơ bản hoạt động tốt</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Thành công</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H13" t="str">
+        <v>playwright-report</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Bot</v>
+      </c>
+      <c r="J13" t="str">
+        <v>14/8/2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J13"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/testmoinhat.xlsx
+++ b/testmoinhat.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Test_Results" sheetId="1" r:id="rId1"/>
+    <sheet name="Test_Results_Full" sheetId="1" r:id="rId1"/>
     <sheet name="Demo_Script" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
@@ -398,14 +398,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J66"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="3" max="3" width="60.83203125" customWidth="1"/>
     <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="30.83203125" customWidth="1"/>
+    <col min="5" max="5" width="35.83203125" customWidth="1"/>
+    <col min="6" max="6" width="35.83203125" customWidth="1"/>
     <col min="7" max="7" width="15.83203125" customWidth="1"/>
     <col min="8" max="8" width="30.83203125" customWidth="1"/>
     <col min="9" max="9" width="15.83203125" customWidth="1"/>
@@ -420,7 +420,7 @@
         <v>Module</v>
       </c>
       <c r="C1" t="str">
-        <v>Scenario</v>
+        <v>Test Name</v>
       </c>
       <c r="D1" t="str">
         <v>Role</v>
@@ -435,7 +435,7 @@
         <v>Status (Pass/Fail)</v>
       </c>
       <c r="H1" t="str">
-        <v>Evidence (Link/Img)</v>
+        <v>Evidence (File)</v>
       </c>
       <c r="I1" t="str">
         <v>Tester</v>
@@ -449,28 +449,28 @@
         <v>TC_E2E_001</v>
       </c>
       <c r="B2" t="str">
-        <v>Auth</v>
+        <v>ai-action-composer</v>
       </c>
       <c r="C2" t="str">
-        <v>public login page renders correctly</v>
+        <v>TEST-ACTION-E2E unified AI assistant shows real progress, editable review and execution receipt</v>
       </c>
       <c r="D2" t="str">
-        <v>Guest</v>
+        <v>All</v>
       </c>
       <c r="E2" t="str">
-        <v>Trang hiển thị đầy đủ</v>
+        <v>Chức năng hoạt động bình thường</v>
       </c>
       <c r="F2" t="str">
-        <v>Đúng như mong đợi</v>
+        <v>Lỗi lệch dữ liệu mock/seed hoặc timeout</v>
       </c>
       <c r="G2" t="str">
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="H2" t="str">
-        <v>Playwright Automated</v>
+        <v>ai-action-composer.spec.ts</v>
       </c>
       <c r="I2" t="str">
-        <v>Bot</v>
+        <v>Playwright Bot</v>
       </c>
       <c r="J2" t="str">
         <v>14/8/2026</v>
@@ -481,28 +481,28 @@
         <v>TC_E2E_002</v>
       </c>
       <c r="B3" t="str">
-        <v>Auth</v>
+        <v>ai-action-composer</v>
       </c>
       <c r="C3" t="str">
-        <v>seeded admin can login and see authenticated shell</v>
+        <v>TEST-ACTION-LIVE-WORKER-01 live worker claims Action Composer job and persists a reviewable draft</v>
       </c>
       <c r="D3" t="str">
-        <v>Admin</v>
+        <v>All</v>
       </c>
       <c r="E3" t="str">
-        <v>Đăng nhập thành công</v>
+        <v>Chức năng hoạt động bình thường</v>
       </c>
       <c r="F3" t="str">
-        <v>Đúng như mong đợi</v>
+        <v>Vượt qua thành công</v>
       </c>
       <c r="G3" t="str">
         <v>Pass</v>
       </c>
       <c r="H3" t="str">
-        <v>Playwright Automated</v>
+        <v>ai-action-composer.spec.ts</v>
       </c>
       <c r="I3" t="str">
-        <v>Bot</v>
+        <v>Playwright Bot</v>
       </c>
       <c r="J3" t="str">
         <v>14/8/2026</v>
@@ -513,28 +513,28 @@
         <v>TC_E2E_003</v>
       </c>
       <c r="B4" t="str">
-        <v>Dashboard</v>
+        <v>ai-action-composer</v>
       </c>
       <c r="C4" t="str">
-        <v>dashboard renders seeded demo data</v>
+        <v>TEST-UA-E2E chat function call opens the canonical task composer without mutating data</v>
       </c>
       <c r="D4" t="str">
-        <v>Admin</v>
+        <v>All</v>
       </c>
       <c r="E4" t="str">
-        <v>Hiển thị dữ liệu demo</v>
+        <v>Chức năng hoạt động bình thường</v>
       </c>
       <c r="F4" t="str">
-        <v>Đúng như mong đợi</v>
+        <v>Vượt qua thành công</v>
       </c>
       <c r="G4" t="str">
         <v>Pass</v>
       </c>
       <c r="H4" t="str">
-        <v>Playwright Automated</v>
+        <v>ai-action-composer.spec.ts</v>
       </c>
       <c r="I4" t="str">
-        <v>Bot</v>
+        <v>Playwright Bot</v>
       </c>
       <c r="J4" t="str">
         <v>14/8/2026</v>
@@ -545,28 +545,28 @@
         <v>TC_E2E_004</v>
       </c>
       <c r="B5" t="str">
-        <v>Navigation</v>
+        <v>ai-activity</v>
       </c>
       <c r="C5" t="str">
-        <v>primary authenticated navigation routes render</v>
+        <v>AI Activity polls a job and restores its deep link after refresh</v>
       </c>
       <c r="D5" t="str">
-        <v>Admin</v>
+        <v>All</v>
       </c>
       <c r="E5" t="str">
-        <v>Các trang chuyển hướng thành công</v>
+        <v>Chức năng hoạt động bình thường</v>
       </c>
       <c r="F5" t="str">
-        <v>Đúng như mong đợi</v>
+        <v>Vượt qua thành công</v>
       </c>
       <c r="G5" t="str">
         <v>Pass</v>
       </c>
       <c r="H5" t="str">
-        <v>Playwright Automated</v>
+        <v>ai-activity.spec.ts</v>
       </c>
       <c r="I5" t="str">
-        <v>Bot</v>
+        <v>Playwright Bot</v>
       </c>
       <c r="J5" t="str">
         <v>14/8/2026</v>
@@ -577,28 +577,28 @@
         <v>TC_E2E_005</v>
       </c>
       <c r="B6" t="str">
-        <v>Project</v>
+        <v>ai-activity</v>
       </c>
       <c r="C6" t="str">
-        <v>projects page shows seeded project or empty-state safely</v>
+        <v>draft review shows the original diff and mutates only after confirmation</v>
       </c>
       <c r="D6" t="str">
-        <v>Admin</v>
+        <v>All</v>
       </c>
       <c r="E6" t="str">
-        <v>Hiển thị danh sách dự án</v>
+        <v>Chức năng hoạt động bình thường</v>
       </c>
       <c r="F6" t="str">
-        <v>Đúng như mong đợi</v>
+        <v>Vượt qua thành công</v>
       </c>
       <c r="G6" t="str">
         <v>Pass</v>
       </c>
       <c r="H6" t="str">
-        <v>Playwright Automated</v>
+        <v>ai-activity.spec.ts</v>
       </c>
       <c r="I6" t="str">
-        <v>Bot</v>
+        <v>Playwright Bot</v>
       </c>
       <c r="J6" t="str">
         <v>14/8/2026</v>
@@ -609,28 +609,28 @@
         <v>TC_E2E_006</v>
       </c>
       <c r="B7" t="str">
-        <v>Project Launch</v>
+        <v>ai-assistant-goal-planner</v>
       </c>
       <c r="C7" t="str">
-        <v>AI Planner creates project &amp; sprint</v>
+        <v>TEST-GS-E2E reload renders goal, selected skill, work plan and safe activity</v>
       </c>
       <c r="D7" t="str">
-        <v>PM</v>
+        <v>All</v>
       </c>
       <c r="E7" t="str">
-        <v>Dự án và Sprint được tạo</v>
+        <v>Chức năng hoạt động bình thường</v>
       </c>
       <c r="F7" t="str">
-        <v>Lỗi hiển thị receipt</v>
+        <v>Vượt qua thành công</v>
       </c>
       <c r="G7" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="H7" t="str">
-        <v>ai-action-composer.spec.ts</v>
+        <v>ai-assistant-goal-planner.spec.ts</v>
       </c>
       <c r="I7" t="str">
-        <v>Bot</v>
+        <v>Playwright Bot</v>
       </c>
       <c r="J7" t="str">
         <v>14/8/2026</v>
@@ -641,28 +641,28 @@
         <v>TC_E2E_007</v>
       </c>
       <c r="B8" t="str">
-        <v>Skill Assignment</v>
+        <v>ai-assistant-workspace</v>
       </c>
       <c r="C8" t="str">
-        <v>AI auto-assign task theo skill</v>
+        <v>TEST-AW-01..07 desktop workspace resizes, persists, resets and keeps the empty composer at the bottom</v>
       </c>
       <c r="D8" t="str">
-        <v>PM, Member</v>
+        <v>All</v>
       </c>
       <c r="E8" t="str">
-        <v>Task gán đúng người</v>
+        <v>Chức năng hoạt động bình thường</v>
       </c>
       <c r="F8" t="str">
-        <v>Đúng như mong đợi</v>
+        <v>Vượt qua thành công</v>
       </c>
       <c r="G8" t="str">
         <v>Pass</v>
       </c>
       <c r="H8" t="str">
-        <v>member-skill-assignment.spec.ts</v>
+        <v>ai-assistant-workspace.spec.ts</v>
       </c>
       <c r="I8" t="str">
-        <v>Bot</v>
+        <v>Playwright Bot</v>
       </c>
       <c r="J8" t="str">
         <v>14/8/2026</v>
@@ -673,28 +673,28 @@
         <v>TC_E2E_008</v>
       </c>
       <c r="B9" t="str">
-        <v>Safety Workflow</v>
+        <v>ai-assistant-workspace</v>
       </c>
       <c r="C9" t="str">
-        <v>QA review và duyệt task</v>
+        <v>TEST-AW-08..10 mobile workspace is full-screen, has no resize controls and keeps submit reachable</v>
       </c>
       <c r="D9" t="str">
-        <v>QA, Member</v>
+        <v>All</v>
       </c>
       <c r="E9" t="str">
-        <v>Trạng thái cập nhật đúng</v>
+        <v>Chức năng hoạt động bình thường</v>
       </c>
       <c r="F9" t="str">
-        <v>Đúng như mong đợi</v>
+        <v>Vượt qua thành công</v>
       </c>
       <c r="G9" t="str">
         <v>Pass</v>
       </c>
       <c r="H9" t="str">
-        <v>rc-safety-workflow.spec.ts</v>
+        <v>ai-assistant-workspace.spec.ts</v>
       </c>
       <c r="I9" t="str">
-        <v>Bot</v>
+        <v>Playwright Bot</v>
       </c>
       <c r="J9" t="str">
         <v>14/8/2026</v>
@@ -705,28 +705,28 @@
         <v>TC_E2E_009</v>
       </c>
       <c r="B10" t="str">
-        <v>Privacy Retention</v>
+        <v>ai-assistant-workspace</v>
       </c>
       <c r="C10" t="str">
-        <v>Kiểm tra mask dữ liệu nhạy cảm</v>
+        <v>TEST-AS-E2E reload restores the canonical turn and safe process steps from the server</v>
       </c>
       <c r="D10" t="str">
-        <v>Admin, Member</v>
+        <v>All</v>
       </c>
       <c r="E10" t="str">
-        <v>Dữ liệu được che giấu</v>
+        <v>Chức năng hoạt động bình thường</v>
       </c>
       <c r="F10" t="str">
-        <v>Đúng như mong đợi</v>
+        <v>Vượt qua thành công</v>
       </c>
       <c r="G10" t="str">
         <v>Pass</v>
       </c>
       <c r="H10" t="str">
-        <v>privacy-retention.spec.ts</v>
+        <v>ai-assistant-workspace.spec.ts</v>
       </c>
       <c r="I10" t="str">
-        <v>Bot</v>
+        <v>Playwright Bot</v>
       </c>
       <c r="J10" t="str">
         <v>14/8/2026</v>
@@ -737,28 +737,28 @@
         <v>TC_E2E_010</v>
       </c>
       <c r="B11" t="str">
-        <v>AI Grounding</v>
+        <v>ai-native-bounded-loop-progressive-launch</v>
       </c>
       <c r="C11" t="str">
-        <v>AI preserves exact selected-message grounding</v>
+        <v>TEST-AI-NATIVE-LOOP-E2E reload renders verified launch brief and progressive reply creates revision</v>
       </c>
       <c r="D11" t="str">
-        <v>Member</v>
+        <v>All</v>
       </c>
       <c r="E11" t="str">
-        <v>AI đọc đúng message</v>
+        <v>Chức năng hoạt động bình thường</v>
       </c>
       <c r="F11" t="str">
-        <v>Fail do model timeout</v>
+        <v>Vượt qua thành công</v>
       </c>
       <c r="G11" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="H11" t="str">
-        <v>ai-native-grounded-surfaces.spec.ts</v>
+        <v>ai-native-bounded-loop-progressive-launch.spec.ts</v>
       </c>
       <c r="I11" t="str">
-        <v>Bot</v>
+        <v>Playwright Bot</v>
       </c>
       <c r="J11" t="str">
         <v>14/8/2026</v>
@@ -769,28 +769,28 @@
         <v>TC_E2E_011</v>
       </c>
       <c r="B12" t="str">
-        <v>Demo Script</v>
+        <v>ai-native-bounded-loop-progressive-launch</v>
       </c>
       <c r="C12" t="str">
-        <v>Chạy xuyên suốt kịch bản 30p</v>
+        <v>TEST-AI-NATIVE-RESUME-E2E canceled durable turn can be resumed after reload</v>
       </c>
       <c r="D12" t="str">
         <v>All</v>
       </c>
       <c r="E12" t="str">
-        <v>Hoàn thành đúng kịch bản</v>
+        <v>Chức năng hoạt động bình thường</v>
       </c>
       <c r="F12" t="str">
-        <v>Fail (Expected &lt;=8 members, got 10)</v>
+        <v>Vượt qua thành công</v>
       </c>
       <c r="G12" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="H12" t="str">
-        <v>demo-script-30-minutes.spec.ts</v>
+        <v>ai-native-bounded-loop-progressive-launch.spec.ts</v>
       </c>
       <c r="I12" t="str">
-        <v>Bot</v>
+        <v>Playwright Bot</v>
       </c>
       <c r="J12" t="str">
         <v>14/8/2026</v>
@@ -801,36 +801,1732 @@
         <v>TC_E2E_012</v>
       </c>
       <c r="B13" t="str">
-        <v>General</v>
+        <v>ai-native-capability-navigation</v>
       </c>
       <c r="C13" t="str">
-        <v>Tổng hợp 53 test cases khác</v>
+        <v>TEST-AI-NATIVE-NAV-01 capability overview renders consistent navigation cards and opens the target route</v>
       </c>
       <c r="D13" t="str">
         <v>All</v>
       </c>
       <c r="E13" t="str">
-        <v>Các luồng cơ bản hoạt động tốt</v>
+        <v>Chức năng hoạt động bình thường</v>
       </c>
       <c r="F13" t="str">
-        <v>Thành công</v>
+        <v>Vượt qua thành công</v>
       </c>
       <c r="G13" t="str">
         <v>Pass</v>
       </c>
       <c r="H13" t="str">
-        <v>playwright-report</v>
+        <v>ai-native-capability-navigation.spec.ts</v>
       </c>
       <c r="I13" t="str">
-        <v>Bot</v>
+        <v>Playwright Bot</v>
       </c>
       <c r="J13" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>TC_E2E_013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>ai-native-capability-navigation</v>
+      </c>
+      <c r="C14" t="str">
+        <v>TEST-AI-NATIVE-NAV-LIVE-01 live session routes capability overview then Project Launch without grounded fallback</v>
+      </c>
+      <c r="D14" t="str">
+        <v>All</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Lỗi lệch dữ liệu mock/seed hoặc timeout</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="H14" t="str">
+        <v>ai-native-capability-navigation.spec.ts</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J14" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>TC_E2E_014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>ai-native-capability-navigation</v>
+      </c>
+      <c r="C15" t="str">
+        <v>TEST-AI-NATIVE-SESSION-LIVE-01 lists real sessions, switches context, and restores the selected session after reload</v>
+      </c>
+      <c r="D15" t="str">
+        <v>All</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H15" t="str">
+        <v>ai-native-capability-navigation.spec.ts</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J15" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>TC_E2E_015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>ai-native-grounded-surfaces</v>
+      </c>
+      <c r="C16" t="str">
+        <v>TEST-CAND-009-E2E renders and restores a tenant-scoped grounded strategic brief</v>
+      </c>
+      <c r="D16" t="str">
+        <v>All</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Lỗi lệch dữ liệu mock/seed hoặc timeout</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="H16" t="str">
+        <v>ai-native-grounded-surfaces.spec.ts</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J16" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>TC_E2E_016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>ai-native-grounded-surfaces</v>
+      </c>
+      <c r="C17" t="str">
+        <v>TEST-CAND-007-E2E preserves exact selected-message grounding and reload read-back</v>
+      </c>
+      <c r="D17" t="str">
+        <v>All</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H17" t="str">
+        <v>ai-native-grounded-surfaces.spec.ts</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J17" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>TC_E2E_017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>ai-native-grounded-surfaces</v>
+      </c>
+      <c r="C18" t="str">
+        <v>TEST-CAND-010-E2E renders grounded meeting checknote from durable read-back</v>
+      </c>
+      <c r="D18" t="str">
+        <v>All</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Lỗi lệch dữ liệu mock/seed hoặc timeout</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="H18" t="str">
+        <v>ai-native-grounded-surfaces.spec.ts</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J18" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>TC_E2E_018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>ai-native-next-candidates</v>
+      </c>
+      <c r="C19" t="str">
+        <v>TEST-PORTFOLIO-SCHEDULE-E2E native capacity board keeps schedule changes in review until confirm</v>
+      </c>
+      <c r="D19" t="str">
+        <v>All</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H19" t="str">
+        <v>ai-native-next-candidates.spec.ts</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J19" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>TC_E2E_019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>ai-native-next-candidates</v>
+      </c>
+      <c r="C20" t="str">
+        <v>TEST-TASK-DRAFT-E2E reload restores source-linked draft and selective confirm shows receipt</v>
+      </c>
+      <c r="D20" t="str">
+        <v>All</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Lỗi lệch dữ liệu mock/seed hoặc timeout</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="H20" t="str">
+        <v>ai-native-next-candidates.spec.ts</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J20" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>TC_E2E_020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>ai-project-launch-orchestration</v>
+      </c>
+      <c r="C21" t="str">
+        <v>TEST-PL-BCD-E2E review card confirms with idempotency receipt then produces review-only replan</v>
+      </c>
+      <c r="D21" t="str">
+        <v>All</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Lỗi lệch dữ liệu mock/seed hoặc timeout</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="H21" t="str">
+        <v>ai-project-launch-orchestration.spec.ts</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J21" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>TC_E2E_021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>ai-research-plan</v>
+      </c>
+      <c r="C22" t="str">
+        <v>TEST-RP-E2E reload renders grounded plan and gates action adapters</v>
+      </c>
+      <c r="D22" t="str">
+        <v>All</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Lỗi lệch dữ liệu mock/seed hoặc timeout</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="H22" t="str">
+        <v>ai-research-plan.spec.ts</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J22" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>TC_E2E_022</v>
+      </c>
+      <c r="B23" t="str">
+        <v>ai-usage-budget</v>
+      </c>
+      <c r="C23" t="str">
+        <v>admin reviews, confirms and reloads a grounded AI budget policy</v>
+      </c>
+      <c r="D23" t="str">
+        <v>All</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Lỗi lệch dữ liệu mock/seed hoặc timeout</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="H23" t="str">
+        <v>ai-usage-budget.spec.ts</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J23" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>TC_E2E_023</v>
+      </c>
+      <c r="B24" t="str">
+        <v>ai-usage-budget</v>
+      </c>
+      <c r="C24" t="str">
+        <v>stale confirmation reloads the winner and requires a new review</v>
+      </c>
+      <c r="D24" t="str">
+        <v>All</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H24" t="str">
+        <v>ai-usage-budget.spec.ts</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J24" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>TC_E2E_024</v>
+      </c>
+      <c r="B25" t="str">
+        <v>ai-usage-budget</v>
+      </c>
+      <c r="C25" t="str">
+        <v>ledger failure retries to an honest empty and read-only state</v>
+      </c>
+      <c r="D25" t="str">
+        <v>All</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H25" t="str">
+        <v>ai-usage-budget.spec.ts</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J25" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>TC_E2E_025</v>
+      </c>
+      <c r="B26" t="str">
+        <v>ai-usage-budget</v>
+      </c>
+      <c r="C26" t="str">
+        <v>unauthorized user sees permission state without ledger disclosure</v>
+      </c>
+      <c r="D26" t="str">
+        <v>All</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H26" t="str">
+        <v>ai-usage-budget.spec.ts</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J26" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>TC_E2E_026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>basic-seed-navigation</v>
+      </c>
+      <c r="C27" t="str">
+        <v>TC-E2E-001 public login page renders correctly</v>
+      </c>
+      <c r="D27" t="str">
+        <v>All</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H27" t="str">
+        <v>basic-seed-navigation.spec.ts</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J27" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>TC_E2E_027</v>
+      </c>
+      <c r="B28" t="str">
+        <v>basic-seed-navigation</v>
+      </c>
+      <c r="C28" t="str">
+        <v>TC-E2E-002 seeded admin can login and see authenticated shell</v>
+      </c>
+      <c r="D28" t="str">
+        <v>All</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H28" t="str">
+        <v>basic-seed-navigation.spec.ts</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J28" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>TC_E2E_028</v>
+      </c>
+      <c r="B29" t="str">
+        <v>basic-seed-navigation</v>
+      </c>
+      <c r="C29" t="str">
+        <v>TC-E2E-003 dashboard renders seeded demo data</v>
+      </c>
+      <c r="D29" t="str">
+        <v>All</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H29" t="str">
+        <v>basic-seed-navigation.spec.ts</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J29" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>TC_E2E_029</v>
+      </c>
+      <c r="B30" t="str">
+        <v>basic-seed-navigation</v>
+      </c>
+      <c r="C30" t="str">
+        <v>TC-E2E-004 primary authenticated navigation routes render</v>
+      </c>
+      <c r="D30" t="str">
+        <v>All</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H30" t="str">
+        <v>basic-seed-navigation.spec.ts</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J30" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>TC_E2E_030</v>
+      </c>
+      <c r="B31" t="str">
+        <v>basic-seed-navigation</v>
+      </c>
+      <c r="C31" t="str">
+        <v>TC-E2E-005 projects page shows seeded project or empty-state safely</v>
+      </c>
+      <c r="D31" t="str">
+        <v>All</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H31" t="str">
+        <v>basic-seed-navigation.spec.ts</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J31" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>TC_E2E_031</v>
+      </c>
+      <c r="B32" t="str">
+        <v>browser-console</v>
+      </c>
+      <c r="C32" t="str">
+        <v>public authentication pages have no browser errors</v>
+      </c>
+      <c r="D32" t="str">
+        <v>All</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H32" t="str">
+        <v>browser-console.spec.ts</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J32" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>TC_E2E_032</v>
+      </c>
+      <c r="B33" t="str">
+        <v>browser-console</v>
+      </c>
+      <c r="C33" t="str">
+        <v>main authenticated routes have no browser errors</v>
+      </c>
+      <c r="D33" t="str">
+        <v>All</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H33" t="str">
+        <v>browser-console.spec.ts</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J33" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>TC_E2E_033</v>
+      </c>
+      <c r="B34" t="str">
+        <v>browser-console</v>
+      </c>
+      <c r="C34" t="str">
+        <v>group detail route renders without a blank screen</v>
+      </c>
+      <c r="D34" t="str">
+        <v>All</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H34" t="str">
+        <v>browser-console.spec.ts</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J34" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>TC_E2E_034</v>
+      </c>
+      <c r="B35" t="str">
+        <v>demo-script-30-minutes</v>
+      </c>
+      <c r="C35" t="str">
+        <v>DEMO-30M chạy xuyên suốt đúng kịch bản thuyết trình</v>
+      </c>
+      <c r="D35" t="str">
+        <v>All</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H35" t="str">
+        <v>demo-script-30-minutes.spec.ts</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J35" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>TC_E2E_035</v>
+      </c>
+      <c r="B36" t="str">
+        <v>member-skill-assignment</v>
+      </c>
+      <c r="C36" t="str">
+        <v>TEST-STAFFING-E2E evidence profile and grounded assignee draft remain human controlled</v>
+      </c>
+      <c r="D36" t="str">
+        <v>All</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Lỗi lệch dữ liệu mock/seed hoặc timeout</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="H36" t="str">
+        <v>member-skill-assignment.spec.ts</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J36" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>TC_E2E_036</v>
+      </c>
+      <c r="B37" t="str">
+        <v>minh-task-and-settings</v>
+      </c>
+      <c r="C37" t="str">
+        <v>canonical task opens from project and tasks pages, refresh and back keep the canonical URL</v>
+      </c>
+      <c r="D37" t="str">
+        <v>All</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H37" t="str">
+        <v>minh-task-and-settings.spec.ts</v>
+      </c>
+      <c r="I37" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J37" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>TC_E2E_037</v>
+      </c>
+      <c r="B38" t="str">
+        <v>minh-task-and-settings</v>
+      </c>
+      <c r="C38" t="str">
+        <v>privacy policy writes through API and Settings stays truthful on partial failure</v>
+      </c>
+      <c r="D38" t="str">
+        <v>All</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H38" t="str">
+        <v>minh-task-and-settings.spec.ts</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J38" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>TC_E2E_038</v>
+      </c>
+      <c r="B39" t="str">
+        <v>privacy-retention</v>
+      </c>
+      <c r="C39" t="str">
+        <v>T1-TR-01 Allow: direct Task URL, Group link and Privacy UI use persisted data</v>
+      </c>
+      <c r="D39" t="str">
+        <v>All</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H39" t="str">
+        <v>privacy-retention.spec.ts</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J39" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>TC_E2E_039</v>
+      </c>
+      <c r="B40" t="str">
+        <v>privacy-retention</v>
+      </c>
+      <c r="C40" t="str">
+        <v>T1-TR-01 Deny: unauthenticated Task URL and Group link are blocked</v>
+      </c>
+      <c r="D40" t="str">
+        <v>All</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H40" t="str">
+        <v>privacy-retention.spec.ts</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J40" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>TC_E2E_040</v>
+      </c>
+      <c r="B41" t="str">
+        <v>privacy-retention</v>
+      </c>
+      <c r="C41" t="str">
+        <v>T1-TR-01 Error: malformed URL renders route error page</v>
+      </c>
+      <c r="D41" t="str">
+        <v>All</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H41" t="str">
+        <v>privacy-retention.spec.ts</v>
+      </c>
+      <c r="I41" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J41" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>TC_E2E_041</v>
+      </c>
+      <c r="B42" t="str">
+        <v>project-progress-ai</v>
+      </c>
+      <c r="C42" t="str">
+        <v>native project card creates one minimal request, polls, grounds output, and restores after reload</v>
+      </c>
+      <c r="D42" t="str">
+        <v>All</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H42" t="str">
+        <v>project-progress-ai.spec.ts</v>
+      </c>
+      <c r="I42" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J42" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>TC_E2E_042</v>
+      </c>
+      <c r="B43" t="str">
+        <v>project-progress-ai</v>
+      </c>
+      <c r="C43" t="str">
+        <v>native project card labels provider failure honestly and retries the persisted job</v>
+      </c>
+      <c r="D43" t="str">
+        <v>All</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G43" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H43" t="str">
+        <v>project-progress-ai.spec.ts</v>
+      </c>
+      <c r="I43" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J43" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>TC_E2E_043</v>
+      </c>
+      <c r="B44" t="str">
+        <v>project-progress-ai</v>
+      </c>
+      <c r="C44" t="str">
+        <v>native project card shows deterministic empty state without fabricated insight</v>
+      </c>
+      <c r="D44" t="str">
+        <v>All</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H44" t="str">
+        <v>project-progress-ai.spec.ts</v>
+      </c>
+      <c r="I44" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J44" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>TC_E2E_044</v>
+      </c>
+      <c r="B45" t="str">
+        <v>qaly.smoke</v>
+      </c>
+      <c r="C45" t="str">
+        <v>should login successfully</v>
+      </c>
+      <c r="D45" t="str">
+        <v>All</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G45" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H45" t="str">
+        <v>qaly.smoke.spec.ts</v>
+      </c>
+      <c r="I45" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J45" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>TC_E2E_045</v>
+      </c>
+      <c r="B46" t="str">
+        <v>qaly.smoke</v>
+      </c>
+      <c r="C46" t="str">
+        <v>should show an honest empty state when dashboard data fails</v>
+      </c>
+      <c r="D46" t="str">
+        <v>All</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G46" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H46" t="str">
+        <v>qaly.smoke.spec.ts</v>
+      </c>
+      <c r="I46" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J46" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>TC_E2E_046</v>
+      </c>
+      <c r="B47" t="str">
+        <v>qaly.smoke</v>
+      </c>
+      <c r="C47" t="str">
+        <v>should report webhook secret presence without exposing the secret</v>
+      </c>
+      <c r="D47" t="str">
+        <v>All</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G47" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H47" t="str">
+        <v>qaly.smoke.spec.ts</v>
+      </c>
+      <c r="I47" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J47" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>TC_E2E_047</v>
+      </c>
+      <c r="B48" t="str">
+        <v>qaly.smoke</v>
+      </c>
+      <c r="C48" t="str">
+        <v>should render database-backed Gantt dates on the project timeline</v>
+      </c>
+      <c r="D48" t="str">
+        <v>All</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G48" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H48" t="str">
+        <v>qaly.smoke.spec.ts</v>
+      </c>
+      <c r="I48" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J48" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>TC_E2E_048</v>
+      </c>
+      <c r="B49" t="str">
+        <v>qaly.smoke</v>
+      </c>
+      <c r="C49" t="str">
+        <v>should create a group and open group page</v>
+      </c>
+      <c r="D49" t="str">
+        <v>All</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G49" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H49" t="str">
+        <v>qaly.smoke.spec.ts</v>
+      </c>
+      <c r="I49" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J49" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>TC_E2E_049</v>
+      </c>
+      <c r="B50" t="str">
+        <v>qaly.smoke</v>
+      </c>
+      <c r="C50" t="str">
+        <v>should send a chat message and receive it in a second context</v>
+      </c>
+      <c r="D50" t="str">
+        <v>All</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G50" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H50" t="str">
+        <v>qaly.smoke.spec.ts</v>
+      </c>
+      <c r="I50" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J50" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>TC_E2E_050</v>
+      </c>
+      <c r="B51" t="str">
+        <v>qaly.smoke</v>
+      </c>
+      <c r="C51" t="str">
+        <v>should vote in a group poll</v>
+      </c>
+      <c r="D51" t="str">
+        <v>All</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G51" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H51" t="str">
+        <v>qaly.smoke.spec.ts</v>
+      </c>
+      <c r="I51" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J51" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>TC_E2E_051</v>
+      </c>
+      <c r="B52" t="str">
+        <v>qaly.smoke</v>
+      </c>
+      <c r="C52" t="str">
+        <v>should open analytics page</v>
+      </c>
+      <c r="D52" t="str">
+        <v>All</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G52" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H52" t="str">
+        <v>qaly.smoke.spec.ts</v>
+      </c>
+      <c r="I52" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J52" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>TC_E2E_052</v>
+      </c>
+      <c r="B53" t="str">
+        <v>qaly.smoke</v>
+      </c>
+      <c r="C53" t="str">
+        <v>should render meeting page in two authenticated contexts</v>
+      </c>
+      <c r="D53" t="str">
+        <v>All</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G53" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H53" t="str">
+        <v>qaly.smoke.spec.ts</v>
+      </c>
+      <c r="I53" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J53" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>TC_E2E_053</v>
+      </c>
+      <c r="B54" t="str">
+        <v>qaly.smoke</v>
+      </c>
+      <c r="C54" t="str">
+        <v>should preview and import a Wiki document</v>
+      </c>
+      <c r="D54" t="str">
+        <v>All</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G54" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H54" t="str">
+        <v>qaly.smoke.spec.ts</v>
+      </c>
+      <c r="I54" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J54" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>TC_E2E_054</v>
+      </c>
+      <c r="B55" t="str">
+        <v>rc-safety-workflow</v>
+      </c>
+      <c r="C55" t="str">
+        <v>organization revoke closes project, task, group, meeting, Wiki, AI and analytics deep-links</v>
+      </c>
+      <c r="D55" t="str">
+        <v>All</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G55" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H55" t="str">
+        <v>rc-safety-workflow.spec.ts</v>
+      </c>
+      <c r="I55" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J55" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>TC_E2E_055</v>
+      </c>
+      <c r="B56" t="str">
+        <v>roadmap-ui</v>
+      </c>
+      <c r="C56" t="str">
+        <v>tab lộ trình và popup mẫu dùng giao diện gọn với bảng màu milk/sapphire</v>
+      </c>
+      <c r="D56" t="str">
+        <v>All</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F56" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G56" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H56" t="str">
+        <v>roadmap-ui.spec.ts</v>
+      </c>
+      <c r="I56" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J56" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>TC_E2E_056</v>
+      </c>
+      <c r="B57" t="str">
+        <v>sidebar</v>
+      </c>
+      <c r="C57" t="str">
+        <v>TC-SIDEBAR-001 Sidebar displays correct Admin user info</v>
+      </c>
+      <c r="D57" t="str">
+        <v>All</v>
+      </c>
+      <c r="E57" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F57" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G57" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H57" t="str">
+        <v>sidebar.spec.ts</v>
+      </c>
+      <c r="I57" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J57" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>TC_E2E_057</v>
+      </c>
+      <c r="B58" t="str">
+        <v>sidebar</v>
+      </c>
+      <c r="C58" t="str">
+        <v>TC-SIDEBAR-002 Sidebar displays correct Member user info and handles refresh</v>
+      </c>
+      <c r="D58" t="str">
+        <v>All</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G58" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H58" t="str">
+        <v>sidebar.spec.ts</v>
+      </c>
+      <c r="I58" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J58" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>TC_E2E_058</v>
+      </c>
+      <c r="B59" t="str">
+        <v>sidebar</v>
+      </c>
+      <c r="C59" t="str">
+        <v>TC-SIDEBAR-003 Logout and Login with different account updates Sidebar correctly</v>
+      </c>
+      <c r="D59" t="str">
+        <v>All</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F59" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G59" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H59" t="str">
+        <v>sidebar.spec.ts</v>
+      </c>
+      <c r="I59" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J59" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>TC_E2E_059</v>
+      </c>
+      <c r="B60" t="str">
+        <v>sidebar</v>
+      </c>
+      <c r="C60" t="str">
+        <v>TC-SIDEBAR-004 Sidebar is responsive on Desktop, Tablet, Mobile</v>
+      </c>
+      <c r="D60" t="str">
+        <v>All</v>
+      </c>
+      <c r="E60" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F60" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G60" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H60" t="str">
+        <v>sidebar.spec.ts</v>
+      </c>
+      <c r="I60" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J60" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>TC_E2E_060</v>
+      </c>
+      <c r="B61" t="str">
+        <v>sprint-progress-ai</v>
+      </c>
+      <c r="C61" t="str">
+        <v>timeline renders the real Gantt contract instead of dashboard task dates</v>
+      </c>
+      <c r="D61" t="str">
+        <v>All</v>
+      </c>
+      <c r="E61" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F61" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G61" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H61" t="str">
+        <v>sprint-progress-ai.spec.ts</v>
+      </c>
+      <c r="I61" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J61" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>TC_E2E_061</v>
+      </c>
+      <c r="B62" t="str">
+        <v>sprint-progress-ai</v>
+      </c>
+      <c r="C62" t="str">
+        <v>native sprint card creates a minimal request, renders grounded output, and restores the exact milestone</v>
+      </c>
+      <c r="D62" t="str">
+        <v>All</v>
+      </c>
+      <c r="E62" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F62" t="str">
+        <v>Lỗi lệch dữ liệu mock/seed hoặc timeout</v>
+      </c>
+      <c r="G62" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="H62" t="str">
+        <v>sprint-progress-ai.spec.ts</v>
+      </c>
+      <c r="I62" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J62" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>TC_E2E_062</v>
+      </c>
+      <c r="B63" t="str">
+        <v>sprint-progress-ai</v>
+      </c>
+      <c r="C63" t="str">
+        <v>native sprint card reports provider failure honestly and retries the same persisted job</v>
+      </c>
+      <c r="D63" t="str">
+        <v>All</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F63" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G63" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H63" t="str">
+        <v>sprint-progress-ai.spec.ts</v>
+      </c>
+      <c r="I63" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J63" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>TC_E2E_063</v>
+      </c>
+      <c r="B64" t="str">
+        <v>sprint-progress-ai</v>
+      </c>
+      <c r="C64" t="str">
+        <v>native sprint card supports cancel and deterministic empty without fabricated narrative</v>
+      </c>
+      <c r="D64" t="str">
+        <v>All</v>
+      </c>
+      <c r="E64" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F64" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G64" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H64" t="str">
+        <v>sprint-progress-ai.spec.ts</v>
+      </c>
+      <c r="I64" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J64" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>TC_E2E_064</v>
+      </c>
+      <c r="B65" t="str">
+        <v>task-skills-ai</v>
+      </c>
+      <c r="C65" t="str">
+        <v>task detail creates a canonical draft, supports selective review, confirms, and restores</v>
+      </c>
+      <c r="D65" t="str">
+        <v>All</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F65" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G65" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H65" t="str">
+        <v>task-skills-ai.spec.ts</v>
+      </c>
+      <c r="I65" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J65" t="str">
+        <v>14/8/2026</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>TC_E2E_065</v>
+      </c>
+      <c r="B66" t="str">
+        <v>task-skills-ai</v>
+      </c>
+      <c r="C66" t="str">
+        <v>feature-off state is honest and manual task tagging remains usable</v>
+      </c>
+      <c r="D66" t="str">
+        <v>All</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Chức năng hoạt động bình thường</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Vượt qua thành công</v>
+      </c>
+      <c r="G66" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H66" t="str">
+        <v>task-skills-ai.spec.ts</v>
+      </c>
+      <c r="I66" t="str">
+        <v>Playwright Bot</v>
+      </c>
+      <c r="J66" t="str">
         <v>14/8/2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J66"/>
   </ignoredErrors>
 </worksheet>
 </file>
